--- a/data/dividends_info_20260410.xlsx
+++ b/data/dividends_info_20260410.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>33.41999816894531</v>
+        <v>33.89500045776367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2692998352215059</v>
+        <v>0.2655258851881367</v>
       </c>
       <c r="J2" t="n">
         <v>339</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>53.25</v>
+        <v>53.04999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.314553990610329</v>
+        <v>1.319509915300776</v>
       </c>
       <c r="J3" t="n">
         <v>318</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>33.40000152587891</v>
+        <v>33.89500045776367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2694610655339833</v>
+        <v>0.2655258851881367</v>
       </c>
       <c r="J6" t="n">
         <v>248</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.089999914169312</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I7" t="n">
-        <v>3.68421067761643</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J7" t="n">
         <v>227</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.920000076293945</v>
+        <v>5.960000038146973</v>
       </c>
       <c r="I8" t="n">
-        <v>3.378378334839559</v>
+        <v>3.355704676508394</v>
       </c>
       <c r="J8" t="n">
         <v>220</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>33.40000152587891</v>
+        <v>33.89500045776367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2694610655339833</v>
+        <v>0.2655258851881367</v>
       </c>
       <c r="J11" t="n">
         <v>164</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>16.73999977111816</v>
+        <v>16.55999946594238</v>
       </c>
       <c r="I14" t="n">
-        <v>3.584229439687277</v>
+        <v>3.62318852264441</v>
       </c>
       <c r="J14" t="n">
         <v>101</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.28000020980835</v>
+        <v>5.230000019073486</v>
       </c>
       <c r="I17" t="n">
-        <v>2.272727182417209</v>
+        <v>2.29445505855387</v>
       </c>
       <c r="J17" t="n">
         <v>94</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.519999980926514</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="I20" t="n">
-        <v>1.548672572906767</v>
+        <v>1.538461473969618</v>
       </c>
       <c r="J20" t="n">
         <v>87</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>32.29999923706055</v>
+        <v>32.25</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4643962957989553</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="J21" t="n">
         <v>87</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>23.55999946594238</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="I23" t="n">
-        <v>1.061120567347178</v>
+        <v>1.059322016775454</v>
       </c>
       <c r="J23" t="n">
         <v>73</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>24.72500038146973</v>
+        <v>24.89999961853027</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7886754175589162</v>
+        <v>0.7831325421181269</v>
       </c>
       <c r="J24" t="n">
         <v>73</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.845000028610229</v>
+        <v>1.894999980926514</v>
       </c>
       <c r="I25" t="n">
-        <v>1.788617858442944</v>
+        <v>1.741424819638545</v>
       </c>
       <c r="J25" t="n">
         <v>73</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.420000076293945</v>
+        <v>5.40500020980835</v>
       </c>
       <c r="I26" t="n">
-        <v>5.350553430218666</v>
+        <v>5.365402196909125</v>
       </c>
       <c r="J26" t="n">
         <v>73</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.173999786376953</v>
+        <v>4.171999931335449</v>
       </c>
       <c r="I27" t="n">
-        <v>3.833253670069796</v>
+        <v>3.835091146532793</v>
       </c>
       <c r="J27" t="n">
         <v>73</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.621999979019165</v>
+        <v>2.615999937057495</v>
       </c>
       <c r="I28" t="n">
-        <v>5.286041232229428</v>
+        <v>5.298165265091663</v>
       </c>
       <c r="J28" t="n">
         <v>73</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>57.93999862670898</v>
+        <v>56.31000137329102</v>
       </c>
       <c r="I29" t="n">
-        <v>1.087331748243406</v>
+        <v>1.118806579001118</v>
       </c>
       <c r="J29" t="n">
         <v>73</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>18.14999961853027</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="I30" t="n">
-        <v>4.297520751480665</v>
+        <v>4.406779471067463</v>
       </c>
       <c r="J30" t="n">
         <v>73</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>21.6299991607666</v>
+        <v>21.55999946594238</v>
       </c>
       <c r="I31" t="n">
-        <v>3.9297273831696</v>
+        <v>3.942486183001613</v>
       </c>
       <c r="J31" t="n">
         <v>73</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>33.40000152587891</v>
+        <v>33.89500045776367</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2694610655339833</v>
+        <v>0.2655258851881367</v>
       </c>
       <c r="J32" t="n">
         <v>73</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6.809999942779541</v>
+        <v>6.797999858856201</v>
       </c>
       <c r="I33" t="n">
-        <v>2.662261402692484</v>
+        <v>2.666960926217269</v>
       </c>
       <c r="J33" t="n">
         <v>73</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8.25</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="I34" t="n">
-        <v>3.151515151515152</v>
+        <v>3.19018419839984</v>
       </c>
       <c r="J34" t="n">
         <v>73</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10.30500030517578</v>
+        <v>10.31999969482422</v>
       </c>
       <c r="I35" t="n">
-        <v>2.688015446839669</v>
+        <v>2.684108606504355</v>
       </c>
       <c r="J35" t="n">
         <v>73</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4.038000106811523</v>
+        <v>4.026000022888184</v>
       </c>
       <c r="I36" t="n">
-        <v>2.724120779849557</v>
+        <v>2.73224042162543</v>
       </c>
       <c r="J36" t="n">
         <v>66</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.539999961853027</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9448819039544819</v>
+        <v>0.8888888731905467</v>
       </c>
       <c r="J37" t="n">
         <v>66</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>28.20000076293945</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="I38" t="n">
-        <v>3.936170106274487</v>
+        <v>3.943161687538076</v>
       </c>
       <c r="J38" t="n">
         <v>55</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.8820000290870667</v>
       </c>
       <c r="I39" t="n">
-        <v>3.409090927563422</v>
+        <v>3.401360432045807</v>
       </c>
       <c r="J39" t="n">
         <v>52</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.5279999971389771</v>
+        <v>0.5320000052452087</v>
       </c>
       <c r="I40" t="n">
-        <v>4.356060629664374</v>
+        <v>4.323308228051402</v>
       </c>
       <c r="J40" t="n">
         <v>52</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.660000085830688</v>
+        <v>2.650000095367432</v>
       </c>
       <c r="I41" t="n">
-        <v>6.766917074883777</v>
+        <v>6.792452585743865</v>
       </c>
       <c r="J41" t="n">
         <v>45</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8.5</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="I42" t="n">
-        <v>3.529411764705882</v>
+        <v>3.448275937667407</v>
       </c>
       <c r="J42" t="n">
         <v>45</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>12.67000007629395</v>
+        <v>13.07999992370605</v>
       </c>
       <c r="I43" t="n">
-        <v>1.973164944708718</v>
+        <v>1.911314995857933</v>
       </c>
       <c r="J43" t="n">
         <v>45</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.460000038146973</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8670520135620203</v>
+        <v>0.8823529164271378</v>
       </c>
       <c r="J44" t="n">
         <v>45</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3.630000114440918</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="I45" t="n">
-        <v>4.132231274684204</v>
+        <v>3.947368470585578</v>
       </c>
       <c r="J45" t="n">
         <v>45</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.530999898910522</v>
+        <v>2.532999992370605</v>
       </c>
       <c r="I47" t="n">
-        <v>4.109047971308381</v>
+        <v>4.105803407550254</v>
       </c>
       <c r="J47" t="n">
         <v>38</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.406000137329102</v>
+        <v>9.196000099182129</v>
       </c>
       <c r="I48" t="n">
-        <v>3.083138377269336</v>
+        <v>3.153544985561624</v>
       </c>
       <c r="J48" t="n">
         <v>38</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.089999914169312</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I49" t="n">
-        <v>3.68421067761643</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J49" t="n">
         <v>38</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>36.20999908447266</v>
+        <v>35.90000152587891</v>
       </c>
       <c r="I50" t="n">
-        <v>4.529135712415012</v>
+        <v>4.568244931181376</v>
       </c>
       <c r="J50" t="n">
         <v>38</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>34.66999816894531</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="I51" t="n">
-        <v>5.768676393503373</v>
+        <v>5.698005945711313</v>
       </c>
       <c r="J51" t="n">
         <v>38</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.930000066757202</v>
+        <v>3.996000051498413</v>
       </c>
       <c r="I52" t="n">
-        <v>2.544529218863702</v>
+        <v>2.502502470251525</v>
       </c>
       <c r="J52" t="n">
         <v>38</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>35.38000106811523</v>
+        <v>34.56000137329102</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4196155893669361</v>
+        <v>0.4295717421896119</v>
       </c>
       <c r="J53" t="n">
         <v>38</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>22.5</v>
+        <v>22.42000007629395</v>
       </c>
       <c r="I54" t="n">
-        <v>4.088888888888889</v>
+        <v>4.103479022610588</v>
       </c>
       <c r="J54" t="n">
         <v>38</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>8.345000267028809</v>
+        <v>8.439999580383301</v>
       </c>
       <c r="I55" t="n">
-        <v>3.59496693110129</v>
+        <v>3.554502546389648</v>
       </c>
       <c r="J55" t="n">
         <v>38</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>83.41999816894531</v>
+        <v>83.83999633789062</v>
       </c>
       <c r="I56" t="n">
-        <v>1.246703455799355</v>
+        <v>1.240458069450061</v>
       </c>
       <c r="J56" t="n">
         <v>38</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>46.5099983215332</v>
+        <v>49.11000061035156</v>
       </c>
       <c r="I57" t="n">
-        <v>1.505052731158483</v>
+        <v>1.425371597027534</v>
       </c>
       <c r="J57" t="n">
         <v>38</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>53.25</v>
+        <v>53.04999923706055</v>
       </c>
       <c r="I58" t="n">
-        <v>4.131455399061033</v>
+        <v>4.147031162373868</v>
       </c>
       <c r="J58" t="n">
         <v>38</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>7.920000076293945</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="I59" t="n">
-        <v>10.8585857539843</v>
+        <v>10.64356445693559</v>
       </c>
       <c r="J59" t="n">
         <v>38</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>12.13599967956543</v>
+        <v>12.27999973297119</v>
       </c>
       <c r="I60" t="n">
-        <v>4.614370589865183</v>
+        <v>4.560260685482165</v>
       </c>
       <c r="J60" t="n">
         <v>38</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.945000052452087</v>
+        <v>1.940000057220459</v>
       </c>
       <c r="I61" t="n">
-        <v>2.05655521446241</v>
+        <v>2.061855609288493</v>
       </c>
       <c r="J61" t="n">
         <v>38</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>9</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="I62" t="n">
-        <v>3.333333333333333</v>
+        <v>3.253796001208539</v>
       </c>
       <c r="J62" t="n">
         <v>38</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2.269999980926514</v>
+        <v>2.339999914169312</v>
       </c>
       <c r="I63" t="n">
-        <v>4.757709291077578</v>
+        <v>4.61538478467592</v>
       </c>
       <c r="J63" t="n">
         <v>38</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>73</v>
+        <v>74.09999847412109</v>
       </c>
       <c r="I64" t="n">
-        <v>2.821917808219178</v>
+        <v>2.780027047800063</v>
       </c>
       <c r="J64" t="n">
         <v>38</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>15.38000011444092</v>
+        <v>15.64000034332275</v>
       </c>
       <c r="I65" t="n">
-        <v>4.876462902596431</v>
+        <v>4.795396314170802</v>
       </c>
       <c r="J65" t="n">
         <v>38</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>15.75</v>
+        <v>16.6299991607666</v>
       </c>
       <c r="I66" t="n">
-        <v>1.904761904761905</v>
+        <v>1.803968822245994</v>
       </c>
       <c r="J66" t="n">
         <v>38</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>43</v>
+        <v>46.5</v>
       </c>
       <c r="I67" t="n">
-        <v>1.976744186046512</v>
+        <v>1.827956989247312</v>
       </c>
       <c r="J67" t="n">
         <v>38</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>33.70000076293945</v>
+        <v>33.93999862670898</v>
       </c>
       <c r="I68" t="n">
-        <v>2.522255135776618</v>
+        <v>2.504419665270979</v>
       </c>
       <c r="J68" t="n">
         <v>38</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>60.68000030517578</v>
+        <v>61.09999847412109</v>
       </c>
       <c r="I69" t="n">
-        <v>2.142386277953125</v>
+        <v>2.127659627603125</v>
       </c>
       <c r="J69" t="n">
         <v>38</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>7.340000152587891</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I70" t="n">
-        <v>8.174386751047352</v>
+        <v>7.894736941171156</v>
       </c>
       <c r="J70" t="n">
         <v>38</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>5.800000190734863</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I71" t="n">
-        <v>8.103448009377576</v>
+        <v>8.034188165162375</v>
       </c>
       <c r="J71" t="n">
         <v>38</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>5.920000076293945</v>
+        <v>5.960000038146973</v>
       </c>
       <c r="I72" t="n">
-        <v>3.378378334839559</v>
+        <v>3.355704676508394</v>
       </c>
       <c r="J72" t="n">
         <v>38</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>22.44000053405762</v>
+        <v>22.5</v>
       </c>
       <c r="I73" t="n">
-        <v>4.456327879682003</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="J73" t="n">
         <v>38</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>4.329999923706055</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="I74" t="n">
-        <v>4.965358055156295</v>
+        <v>4.919908595661066</v>
       </c>
       <c r="J74" t="n">
         <v>38</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>24.30999946594238</v>
+        <v>23.95000076293945</v>
       </c>
       <c r="I75" t="n">
-        <v>1.110654076230081</v>
+        <v>1.127348607093999</v>
       </c>
       <c r="J75" t="n">
         <v>38</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>9.675000190734863</v>
+        <v>9.75</v>
       </c>
       <c r="I77" t="n">
-        <v>2.480620106135324</v>
+        <v>2.461538461538462</v>
       </c>
       <c r="J77" t="n">
         <v>38</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>20.68000030517578</v>
+        <v>20.77000045776367</v>
       </c>
       <c r="I78" t="n">
-        <v>3.820115997784967</v>
+        <v>3.803562747177041</v>
       </c>
       <c r="J78" t="n">
         <v>38</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>4.730000019073486</v>
+        <v>4.75</v>
       </c>
       <c r="I79" t="n">
-        <v>1.966173353593704</v>
+        <v>1.957894736842105</v>
       </c>
       <c r="J79" t="n">
         <v>38</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>36.70000076293945</v>
+        <v>37.59999847412109</v>
       </c>
       <c r="I81" t="n">
-        <v>0.9536784542888578</v>
+        <v>0.9308511016054803</v>
       </c>
       <c r="J81" t="n">
         <v>38</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>7.489999771118164</v>
+        <v>7.5</v>
       </c>
       <c r="I82" t="n">
-        <v>7.400534271541773</v>
+        <v>7.390666666666666</v>
       </c>
       <c r="J82" t="n">
         <v>38</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>2.049999952316284</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I83" t="n">
-        <v>2.926829336371755</v>
+        <v>2.912621440126959</v>
       </c>
       <c r="J83" t="n">
         <v>38</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>12.44999980926514</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="I84" t="n">
-        <v>1.606425727421799</v>
+        <v>1.619433148359132</v>
       </c>
       <c r="J84" t="n">
         <v>38</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>5.885000228881836</v>
+        <v>5.914999961853027</v>
       </c>
       <c r="I85" t="n">
-        <v>1.750212336348035</v>
+        <v>1.741335598719642</v>
       </c>
       <c r="J85" t="n">
         <v>38</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>5.604000091552734</v>
+        <v>5.657000064849854</v>
       </c>
       <c r="I86" t="n">
-        <v>3.390435347893714</v>
+        <v>3.35867063499924</v>
       </c>
       <c r="J86" t="n">
         <v>38</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>10.56999969482422</v>
+        <v>10.55500030517578</v>
       </c>
       <c r="I87" t="n">
-        <v>4.087038907026044</v>
+        <v>4.092846873610824</v>
       </c>
       <c r="J87" t="n">
         <v>38</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>26.79000091552734</v>
+        <v>26.68000030517578</v>
       </c>
       <c r="I88" t="n">
-        <v>1.64240382591767</v>
+        <v>1.64917539342997</v>
       </c>
       <c r="J88" t="n">
         <v>38</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.049999952316284</v>
+        <v>1.070000052452087</v>
       </c>
       <c r="I89" t="n">
-        <v>2.857142986894471</v>
+        <v>2.803738180315963</v>
       </c>
       <c r="J89" t="n">
         <v>38</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>8.380000114440918</v>
+        <v>8.279999732971191</v>
       </c>
       <c r="I90" t="n">
-        <v>5.608591808848162</v>
+        <v>5.676328685476242</v>
       </c>
       <c r="J90" t="n">
         <v>38</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>54.77999877929688</v>
+        <v>54.38000106811523</v>
       </c>
       <c r="I91" t="n">
-        <v>2.555677311422476</v>
+        <v>2.574475859694062</v>
       </c>
       <c r="J91" t="n">
         <v>38</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>3.469000101089478</v>
+        <v>3.41700005531311</v>
       </c>
       <c r="I92" t="n">
-        <v>8.648025115530602</v>
+        <v>8.779631113365905</v>
       </c>
       <c r="J92" t="n">
         <v>38</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3.579999923706055</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="I94" t="n">
-        <v>4.748603453153546</v>
+        <v>4.82954548071485</v>
       </c>
       <c r="J94" t="n">
         <v>38</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>20.14999961853027</v>
+        <v>19.97999954223633</v>
       </c>
       <c r="I95" t="n">
-        <v>3.473945475196279</v>
+        <v>3.503503583772606</v>
       </c>
       <c r="J95" t="n">
         <v>38</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>2.660000085830688</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="I96" t="n">
-        <v>1.315789431227401</v>
+        <v>1.29629627340288</v>
       </c>
       <c r="J96" t="n">
         <v>38</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.9660000205039978</v>
+        <v>0.9750000238418579</v>
       </c>
       <c r="I98" t="n">
-        <v>7.246376657784999</v>
+        <v>7.179487003925837</v>
       </c>
       <c r="J98" t="n">
         <v>38</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>49.13999938964844</v>
+        <v>48.84000015258789</v>
       </c>
       <c r="I99" t="n">
-        <v>1.444851462797463</v>
+        <v>1.453726449184663</v>
       </c>
       <c r="J99" t="n">
         <v>38</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>84.80000305175781</v>
+        <v>83.69999694824219</v>
       </c>
       <c r="I100" t="n">
-        <v>1.591981074783718</v>
+        <v>1.612903284613981</v>
       </c>
       <c r="J100" t="n">
         <v>38</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>7.199999809265137</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="I101" t="n">
-        <v>1.111111140545505</v>
+        <v>1.120448200223526</v>
       </c>
       <c r="J101" t="n">
         <v>38</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>4.182000160217285</v>
+        <v>4.132999897003174</v>
       </c>
       <c r="I103" t="n">
-        <v>4.065040494670074</v>
+        <v>4.113235040805748</v>
       </c>
       <c r="J103" t="n">
         <v>38</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>59.29999923706055</v>
+        <v>58.79999923706055</v>
       </c>
       <c r="I105" t="n">
-        <v>0.7588532981274725</v>
+        <v>0.7653061323789497</v>
       </c>
       <c r="J105" t="n">
         <v>38</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>4.909999847412109</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="I106" t="n">
-        <v>0.8146639764374455</v>
+        <v>0.8602150361211831</v>
       </c>
       <c r="J106" t="n">
         <v>38</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>32.34000015258789</v>
+        <v>32.43999862670898</v>
       </c>
       <c r="I107" t="n">
-        <v>3.246753231434285</v>
+        <v>3.236744896578073</v>
       </c>
       <c r="J107" t="n">
         <v>38</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>19.13999938964844</v>
+        <v>19.5</v>
       </c>
       <c r="I109" t="n">
-        <v>1.985371014199284</v>
+        <v>1.948717948717949</v>
       </c>
       <c r="J109" t="n">
         <v>38</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>25.22999954223633</v>
+        <v>25.45999908447266</v>
       </c>
       <c r="I110" t="n">
-        <v>2.378121327333236</v>
+        <v>2.356637948058385</v>
       </c>
       <c r="J110" t="n">
         <v>38</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>30.14999961853027</v>
+        <v>30.10000038146973</v>
       </c>
       <c r="I111" t="n">
-        <v>1.160862369579895</v>
+        <v>1.162790682937892</v>
       </c>
       <c r="J111" t="n">
         <v>38</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>2.980000019073486</v>
+        <v>2.960000038146973</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5704697950064269</v>
+        <v>0.574324316922725</v>
       </c>
       <c r="J112" t="n">
         <v>38</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>2.825000047683716</v>
+        <v>2.789999961853027</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3539822949100208</v>
+        <v>0.3584229439687277</v>
       </c>
       <c r="J113" t="n">
         <v>38</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>21.3700008392334</v>
+        <v>21.61000061035156</v>
       </c>
       <c r="I114" t="n">
-        <v>5.240991839100825</v>
+        <v>5.182785600956906</v>
       </c>
       <c r="J114" t="n">
         <v>38</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1.330000042915344</v>
+        <v>1.370000004768372</v>
       </c>
       <c r="I115" t="n">
-        <v>7.518796749870864</v>
+        <v>7.299270047587131</v>
       </c>
       <c r="J115" t="n">
         <v>38</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>2.585999965667725</v>
+        <v>2.654000043869019</v>
       </c>
       <c r="I116" t="n">
-        <v>3.132250621630817</v>
+        <v>3.051996935234322</v>
       </c>
       <c r="J116" t="n">
         <v>38</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>2.105999946594238</v>
+        <v>2.072000026702881</v>
       </c>
       <c r="I117" t="n">
-        <v>4.382716160523406</v>
+        <v>4.454633147224161</v>
       </c>
       <c r="J117" t="n">
         <v>38</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>9.399999618530273</v>
+        <v>9.279999732971191</v>
       </c>
       <c r="I118" t="n">
-        <v>3.723404406421921</v>
+        <v>3.771551832663038</v>
       </c>
       <c r="J118" t="n">
         <v>31</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>11.89999961853027</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="I121" t="n">
-        <v>1.680672322783665</v>
+        <v>1.639344287924599</v>
       </c>
       <c r="J121" t="n">
         <v>31</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>16.20000076293945</v>
+        <v>16.3799991607666</v>
       </c>
       <c r="I124" t="n">
-        <v>3.086419607731402</v>
+        <v>3.052503208898818</v>
       </c>
       <c r="J124" t="n">
         <v>31</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>9.399999618530273</v>
+        <v>9.25</v>
       </c>
       <c r="I126" t="n">
-        <v>0.9042553558453239</v>
+        <v>0.9189189189189189</v>
       </c>
       <c r="J126" t="n">
         <v>31</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>4.570000171661377</v>
+        <v>4.5</v>
       </c>
       <c r="I127" t="n">
-        <v>2.078774538983523</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="J127" t="n">
         <v>31</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>1.129999995231628</v>
+        <v>1.149999976158142</v>
       </c>
       <c r="I128" t="n">
-        <v>2.654867267840171</v>
+        <v>2.608695706257524</v>
       </c>
       <c r="J128" t="n">
         <v>31</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>7.699999809265137</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I129" t="n">
-        <v>1.168831197784008</v>
+        <v>1.192052950017741</v>
       </c>
       <c r="J129" t="n">
         <v>31</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>7.150000095367432</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="I131" t="n">
-        <v>3.076923035882762</v>
+        <v>3.047091501288814</v>
       </c>
       <c r="J131" t="n">
         <v>31</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>3.565000057220459</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="I132" t="n">
-        <v>4.488078469338034</v>
+        <v>4.494382094710844</v>
       </c>
       <c r="J132" t="n">
         <v>24</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>23.29999923706055</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="I133" t="n">
-        <v>2.618025836798077</v>
+        <v>2.500000039085013</v>
       </c>
       <c r="J133" t="n">
         <v>24</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>3.039999961853027</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="I134" t="n">
-        <v>4.934210588231972</v>
+        <v>4.901960875977926</v>
       </c>
       <c r="J134" t="n">
         <v>24</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>11.94999980926514</v>
+        <v>12</v>
       </c>
       <c r="I135" t="n">
-        <v>5.857740679269905</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="J135" t="n">
         <v>24</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.130000114440918</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I136" t="n">
-        <v>5.591456665948364</v>
+        <v>5.524891911747554</v>
       </c>
       <c r="J136" t="n">
         <v>24</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>7.949999809265137</v>
+        <v>7.755000114440918</v>
       </c>
       <c r="I137" t="n">
-        <v>3.396226496575949</v>
+        <v>3.481624706841995</v>
       </c>
       <c r="J137" t="n">
         <v>24</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>5.375</v>
+        <v>5.420000076293945</v>
       </c>
       <c r="I138" t="n">
-        <v>6.511627906976744</v>
+        <v>6.457564484746666</v>
       </c>
       <c r="J138" t="n">
         <v>24</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>37.20000076293945</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="I139" t="n">
-        <v>2.956989186666567</v>
+        <v>2.989130496753413</v>
       </c>
       <c r="J139" t="n">
         <v>24</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>18.64999961853027</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I140" t="n">
-        <v>4.021447803434884</v>
+        <v>3.989361864023487</v>
       </c>
       <c r="J140" t="n">
         <v>24</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>10.35000038146973</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I141" t="n">
-        <v>4.154589218855071</v>
+        <v>4.075829310198792</v>
       </c>
       <c r="J141" t="n">
         <v>24</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>4.195000171661377</v>
+        <v>4.275000095367432</v>
       </c>
       <c r="I142" t="n">
-        <v>3.575685193371384</v>
+        <v>3.508771851550278</v>
       </c>
       <c r="J142" t="n">
         <v>24</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>12.19999980926514</v>
+        <v>12.10000038146973</v>
       </c>
       <c r="I143" t="n">
-        <v>1.616139369529026</v>
+        <v>1.629495816396419</v>
       </c>
       <c r="J143" t="n">
         <v>24</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>28.64999961853027</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="I144" t="n">
-        <v>3.839441586898106</v>
+        <v>3.852889770210915</v>
       </c>
       <c r="J144" t="n">
         <v>24</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>19.70000076293945</v>
+        <v>19.65999984741211</v>
       </c>
       <c r="I145" t="n">
-        <v>2.538070967695712</v>
+        <v>2.543235014652435</v>
       </c>
       <c r="J145" t="n">
         <v>24</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>43.90000152587891</v>
+        <v>44.25</v>
       </c>
       <c r="I146" t="n">
-        <v>1.070614996956063</v>
+        <v>1.062146892655367</v>
       </c>
       <c r="J146" t="n">
         <v>24</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>2.619999885559082</v>
+        <v>2.670000076293945</v>
       </c>
       <c r="I147" t="n">
-        <v>4.198473465830976</v>
+        <v>4.119850069543215</v>
       </c>
       <c r="J147" t="n">
         <v>24</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>79.30000305175781</v>
+        <v>78.90000152587891</v>
       </c>
       <c r="I148" t="n">
-        <v>1.51324079926804</v>
+        <v>1.520912518114977</v>
       </c>
       <c r="J148" t="n">
         <v>24</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>23.39999961853027</v>
+        <v>23.25</v>
       </c>
       <c r="I149" t="n">
-        <v>1.153846172656299</v>
+        <v>1.161290322580645</v>
       </c>
       <c r="J149" t="n">
         <v>24</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>10.44999980926514</v>
+        <v>10.5</v>
       </c>
       <c r="I150" t="n">
-        <v>3.636363702735056</v>
+        <v>3.619047619047619</v>
       </c>
       <c r="J150" t="n">
         <v>24</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>27.75</v>
+        <v>27.5</v>
       </c>
       <c r="I151" t="n">
-        <v>1.081081081081081</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="J151" t="n">
         <v>24</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>0.1537999957799911</v>
+        <v>0.1516000032424927</v>
       </c>
       <c r="I152" t="n">
-        <v>4.55136553450457</v>
+        <v>4.617414149261665</v>
       </c>
       <c r="J152" t="n">
         <v>17</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>7.260000228881836</v>
+        <v>7.5</v>
       </c>
       <c r="I153" t="n">
-        <v>2.203856679831575</v>
+        <v>2.133333333333333</v>
       </c>
       <c r="J153" t="n">
         <v>17</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>2.200000047683716</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I154" t="n">
-        <v>2.954545390507408</v>
+        <v>2.941176419820373</v>
       </c>
       <c r="J154" t="n">
         <v>17</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>7.849999904632568</v>
+        <v>7.989999771118164</v>
       </c>
       <c r="I155" t="n">
-        <v>3.184713414486361</v>
+        <v>3.128911228554561</v>
       </c>
       <c r="J155" t="n">
         <v>17</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>6.78000020980835</v>
+        <v>6.760000228881836</v>
       </c>
       <c r="I157" t="n">
-        <v>7.374631040227261</v>
+        <v>7.396449453711106</v>
       </c>
       <c r="J157" t="n">
         <v>10</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>18.43000030517578</v>
+        <v>18.54000091552734</v>
       </c>
       <c r="I158" t="n">
-        <v>3.526858324671093</v>
+        <v>3.505932944456447</v>
       </c>
       <c r="J158" t="n">
         <v>10</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>12.60499954223633</v>
+        <v>12.67500019073486</v>
       </c>
       <c r="I159" t="n">
-        <v>4.284014435626036</v>
+        <v>4.260354965475486</v>
       </c>
       <c r="J159" t="n">
         <v>10</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>6.671999931335449</v>
+        <v>6.662000179290771</v>
       </c>
       <c r="I160" t="n">
-        <v>1.498800974657448</v>
+        <v>1.501050695117902</v>
       </c>
       <c r="J160" t="n">
         <v>10</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>8.300000190734863</v>
+        <v>8.5</v>
       </c>
       <c r="I161" t="n">
-        <v>1.927710799074499</v>
+        <v>1.882352941176471</v>
       </c>
       <c r="J161" t="n">
         <v>10</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>302.8999938964844</v>
+        <v>301.6499938964844</v>
       </c>
       <c r="I162" t="n">
-        <v>1.193463213219945</v>
+        <v>1.198408776113067</v>
       </c>
       <c r="J162" t="n">
         <v>10</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>14.96000003814697</v>
+        <v>14.85999965667725</v>
       </c>
       <c r="I164" t="n">
-        <v>3.910427797515308</v>
+        <v>3.936743025004943</v>
       </c>
       <c r="J164" t="n">
         <v>10</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>17.64999961853027</v>
+        <v>18.07500076293945</v>
       </c>
       <c r="I165" t="n">
-        <v>3.569405176295751</v>
+        <v>3.485477031302465</v>
       </c>
       <c r="J165" t="n">
         <v>10</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>118.1500015258789</v>
+        <v>119.8000030517578</v>
       </c>
       <c r="I166" t="n">
-        <v>0.761743536501664</v>
+        <v>0.7512520676741289</v>
       </c>
       <c r="J166" t="n">
         <v>10</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>66.48999786376953</v>
+        <v>68.51999664306641</v>
       </c>
       <c r="I167" t="n">
-        <v>2.588058437790485</v>
+        <v>2.511383660691012</v>
       </c>
       <c r="J167" t="n">
         <v>10</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="J168" t="n">
         <v>3</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>1.600000023841858</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I169" t="n">
-        <v>3.749999944120646</v>
+        <v>3.821655923277815</v>
       </c>
       <c r="J169" t="n">
         <v>3</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1.919999957084656</v>
+        <v>1.889999985694885</v>
       </c>
       <c r="I170" t="n">
-        <v>1.770833372914544</v>
+        <v>1.798941812557709</v>
       </c>
       <c r="J170" t="n">
         <v>-11</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>24.30999946594238</v>
+        <v>23.95000076293945</v>
       </c>
       <c r="I171" t="n">
-        <v>1.069518740073411</v>
+        <v>1.085594954979406</v>
       </c>
       <c r="J171" t="n">
         <v>-18</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>33.40000152587891</v>
+        <v>33.89500045776367</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2694610655339833</v>
+        <v>0.2655258851881367</v>
       </c>
       <c r="J172" t="n">
         <v>-18</v>
@@ -10293,7 +10293,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10310,7 +10310,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10320,14 +10320,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10344,7 +10344,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10361,7 +10361,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10378,7 +10378,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10388,14 +10388,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10412,7 +10412,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10429,7 +10429,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10446,7 +10446,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10473,14 +10473,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10497,7 +10497,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10507,14 +10507,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10548,7 +10548,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10565,7 +10565,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10582,7 +10582,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10599,7 +10599,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10626,14 +10626,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10643,14 +10643,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10667,7 +10667,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10684,7 +10684,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10701,7 +10701,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10711,14 +10711,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10735,7 +10735,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10752,7 +10752,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10769,7 +10769,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10786,7 +10786,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10803,7 +10803,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10820,7 +10820,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10837,7 +10837,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10871,7 +10871,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10888,7 +10888,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10905,7 +10905,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10915,14 +10915,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10939,7 +10939,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10956,7 +10956,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10966,14 +10966,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10983,14 +10983,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11007,7 +11007,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11017,14 +11017,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11034,14 +11034,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11085,14 +11085,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11102,14 +11102,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11119,14 +11119,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11143,7 +11143,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11153,14 +11153,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11177,7 +11177,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11194,7 +11194,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11204,14 +11204,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11221,14 +11221,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11262,7 +11262,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11279,7 +11279,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11296,7 +11296,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11313,7 +11313,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11323,14 +11323,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11347,7 +11347,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11364,7 +11364,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11381,7 +11381,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11398,7 +11398,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11415,7 +11415,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11425,14 +11425,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11442,14 +11442,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11459,14 +11459,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11483,7 +11483,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11500,7 +11500,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11534,7 +11534,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11551,7 +11551,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11561,14 +11561,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11578,14 +11578,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11602,7 +11602,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11619,7 +11619,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11636,7 +11636,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11653,7 +11653,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11670,7 +11670,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11687,7 +11687,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11704,7 +11704,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11738,7 +11738,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11772,7 +11772,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11789,7 +11789,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11799,14 +11799,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11823,7 +11823,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11840,7 +11840,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11850,14 +11850,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11867,14 +11867,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11891,7 +11891,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11908,7 +11908,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11942,7 +11942,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11952,14 +11952,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11976,7 +11976,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -11986,14 +11986,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12010,7 +12010,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12027,7 +12027,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12037,14 +12037,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12061,7 +12061,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12078,7 +12078,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12095,7 +12095,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12112,7 +12112,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12129,7 +12129,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12146,7 +12146,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12163,7 +12163,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12180,7 +12180,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12197,7 +12197,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12214,7 +12214,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12231,7 +12231,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12248,7 +12248,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12265,7 +12265,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12275,14 +12275,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12299,7 +12299,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12316,7 +12316,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12350,7 +12350,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12367,7 +12367,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12384,7 +12384,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12401,7 +12401,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12418,7 +12418,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12435,7 +12435,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12479,14 +12479,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12503,7 +12503,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12520,7 +12520,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12537,7 +12537,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12554,7 +12554,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12571,7 +12571,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12588,7 +12588,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12605,7 +12605,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12622,7 +12622,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12639,7 +12639,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12656,7 +12656,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12666,14 +12666,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12690,7 +12690,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12707,7 +12707,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12724,7 +12724,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12741,7 +12741,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12775,7 +12775,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12792,7 +12792,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12809,7 +12809,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12826,7 +12826,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12843,7 +12843,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12853,14 +12853,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12877,7 +12877,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12894,7 +12894,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -12911,7 +12911,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -12928,7 +12928,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -12938,14 +12938,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -12962,7 +12962,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -12979,7 +12979,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -12996,7 +12996,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13013,7 +13013,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13030,7 +13030,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13047,7 +13047,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13064,7 +13064,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13081,7 +13081,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13098,7 +13098,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13115,7 +13115,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13132,7 +13132,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13149,7 +13149,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13183,7 +13183,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13193,14 +13193,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13217,7 +13217,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13234,7 +13234,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13251,7 +13251,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13261,14 +13261,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13278,14 +13278,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13295,14 +13295,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13319,7 +13319,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13329,14 +13329,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13353,7 +13353,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13370,7 +13370,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13380,14 +13380,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13404,7 +13404,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13421,7 +13421,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13438,7 +13438,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13455,7 +13455,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13489,7 +13489,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13506,7 +13506,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13523,7 +13523,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13540,7 +13540,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13557,7 +13557,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13567,14 +13567,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13584,14 +13584,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13608,7 +13608,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13625,7 +13625,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13642,7 +13642,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13659,7 +13659,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13676,7 +13676,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13686,14 +13686,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13710,7 +13710,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13727,7 +13727,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13737,14 +13737,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13761,7 +13761,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13778,7 +13778,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13795,7 +13795,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13812,7 +13812,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13829,7 +13829,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13846,7 +13846,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13863,7 +13863,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13873,14 +13873,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13897,7 +13897,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -13914,7 +13914,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -13931,7 +13931,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -13941,14 +13941,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -13958,14 +13958,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -13982,7 +13982,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -13999,7 +13999,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14009,14 +14009,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14026,14 +14026,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14043,14 +14043,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14060,14 +14060,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14084,7 +14084,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14101,7 +14101,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14118,7 +14118,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14135,7 +14135,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14152,7 +14152,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14169,7 +14169,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14186,7 +14186,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14203,7 +14203,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14220,7 +14220,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14237,7 +14237,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14254,7 +14254,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14264,14 +14264,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14288,7 +14288,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14305,7 +14305,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14322,7 +14322,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14339,7 +14339,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14356,7 +14356,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14373,7 +14373,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14390,7 +14390,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14407,7 +14407,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14424,7 +14424,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14441,7 +14441,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14458,7 +14458,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14475,7 +14475,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14492,7 +14492,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14509,7 +14509,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14526,7 +14526,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14560,7 +14560,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14577,7 +14577,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14587,14 +14587,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14611,7 +14611,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14628,7 +14628,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14645,7 +14645,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14662,7 +14662,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14679,7 +14679,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14696,7 +14696,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14706,14 +14706,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14723,14 +14723,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14747,7 +14747,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14764,7 +14764,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14781,7 +14781,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14798,7 +14798,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14815,7 +14815,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14832,7 +14832,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14849,7 +14849,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14866,7 +14866,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14883,7 +14883,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14893,14 +14893,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14917,7 +14917,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -14934,7 +14934,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -14951,7 +14951,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -14968,7 +14968,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -14985,7 +14985,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15002,7 +15002,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15019,7 +15019,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15036,7 +15036,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15070,7 +15070,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15087,7 +15087,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15104,7 +15104,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15114,14 +15114,14 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15138,7 +15138,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15155,7 +15155,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15165,14 +15165,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15189,7 +15189,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15206,7 +15206,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15223,7 +15223,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15240,7 +15240,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15257,7 +15257,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15274,7 +15274,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15291,7 +15291,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15308,7 +15308,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15325,7 +15325,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15335,14 +15335,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15359,7 +15359,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15369,14 +15369,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15386,14 +15386,14 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15427,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15437,14 +15437,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15454,14 +15454,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15478,7 +15478,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15488,14 +15488,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15512,7 +15512,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15529,7 +15529,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15539,14 +15539,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15563,7 +15563,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15580,7 +15580,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15597,7 +15597,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15624,14 +15624,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15641,14 +15641,14 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15665,7 +15665,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15682,7 +15682,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15699,7 +15699,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15709,14 +15709,14 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15726,14 +15726,14 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15743,14 +15743,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -15760,14 +15760,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -15777,14 +15777,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -15801,7 +15801,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -15818,7 +15818,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -15835,7 +15835,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -15845,14 +15845,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -15869,7 +15869,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -15903,7 +15903,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -15920,7 +15920,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -15937,7 +15937,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -15947,14 +15947,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -15964,14 +15964,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -15988,7 +15988,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -15998,14 +15998,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16015,7 +16015,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16039,7 +16039,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16049,14 +16049,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16073,7 +16073,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16083,14 +16083,14 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16100,14 +16100,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16124,7 +16124,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16141,7 +16141,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -16175,7 +16175,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16185,14 +16185,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16202,14 +16202,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16219,14 +16219,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16236,14 +16236,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16253,14 +16253,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16270,14 +16270,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16311,7 +16311,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16321,14 +16321,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16338,14 +16338,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16362,7 +16362,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16372,14 +16372,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16396,7 +16396,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16406,14 +16406,14 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16423,14 +16423,14 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16440,14 +16440,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16464,7 +16464,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16474,14 +16474,14 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16491,14 +16491,14 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16508,14 +16508,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16542,14 +16542,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16559,14 +16559,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16576,14 +16576,14 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16600,7 +16600,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16617,7 +16617,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16634,7 +16634,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16644,14 +16644,14 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16661,14 +16661,14 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16678,14 +16678,14 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16695,14 +16695,14 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16719,7 +16719,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16736,7 +16736,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16753,7 +16753,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16763,14 +16763,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16780,14 +16780,14 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16804,7 +16804,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -16821,7 +16821,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -16831,14 +16831,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -16872,7 +16872,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -16882,14 +16882,14 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -16899,14 +16899,14 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -16916,14 +16916,14 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -16940,7 +16940,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -16950,7 +16950,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -16984,14 +16984,14 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17008,7 +17008,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17025,7 +17025,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17042,7 +17042,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17059,7 +17059,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17069,14 +17069,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17093,7 +17093,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17110,7 +17110,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17120,14 +17120,14 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17144,7 +17144,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17161,7 +17161,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17171,14 +17171,14 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17195,7 +17195,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17205,14 +17205,14 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17222,14 +17222,14 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17239,14 +17239,14 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17256,14 +17256,14 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17280,7 +17280,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17290,14 +17290,14 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17307,14 +17307,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17331,7 +17331,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17348,7 +17348,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -17365,7 +17365,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17382,7 +17382,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17392,14 +17392,14 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17416,7 +17416,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17433,7 +17433,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17443,14 +17443,14 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17460,14 +17460,14 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17477,14 +17477,14 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17494,14 +17494,14 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17511,14 +17511,14 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17528,14 +17528,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17545,14 +17545,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17569,7 +17569,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17579,14 +17579,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17596,14 +17596,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17620,7 +17620,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17630,14 +17630,14 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17647,14 +17647,14 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17664,14 +17664,14 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17688,7 +17688,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17698,14 +17698,14 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -17715,14 +17715,14 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -17739,7 +17739,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17749,14 +17749,14 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -17773,7 +17773,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -17783,14 +17783,14 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -17800,7 +17800,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -17824,7 +17824,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -17862,112 +17862,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Energy Time S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Giglio.com S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>